--- a/teammatch2x3.xlsx
+++ b/teammatch2x3.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Feb 19, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 07, 2026.</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D8">
@@ -548,12 +548,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="D9">
@@ -567,12 +567,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 75</t>
         </is>
       </c>
       <c r="D10">
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="D11" s="5">

--- a/teammatch2x3.xlsx
+++ b/teammatch2x3.xlsx
@@ -529,12 +529,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 31</t>
         </is>
       </c>
       <c r="D8">
@@ -548,12 +548,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="D9">
@@ -567,7 +567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="D11" s="5">

--- a/teammatch2x3.xlsx
+++ b/teammatch2x3.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 07, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 08, 2026.</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name 58</t>
+          <t>Name 61</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 41</t>
         </is>
       </c>
       <c r="D8">
@@ -548,12 +548,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name 57</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="D9">
@@ -567,12 +567,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 75</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="D10">
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 14</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="D11" s="5">

--- a/teammatch2x3.xlsx
+++ b/teammatch2x3.xlsx
@@ -529,12 +529,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name 61</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name 41</t>
+          <t>Name 40</t>
         </is>
       </c>
       <c r="D8">
@@ -548,12 +548,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name 22</t>
+          <t>Name 17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D9">
@@ -567,12 +567,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 22</t>
+          <t>Name 77</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 29</t>
         </is>
       </c>
       <c r="D10">
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Name 14</t>
+          <t>Name 42</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="D11" s="5">

--- a/teammatch2x3.xlsx
+++ b/teammatch2x3.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 08, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 10, 2026.</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name 40</t>
+          <t>Name 53</t>
         </is>
       </c>
       <c r="D8">
@@ -548,12 +548,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name 17</t>
+          <t>Name 59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D9">
@@ -567,12 +567,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 77</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 29</t>
+          <t>Name 56</t>
         </is>
       </c>
       <c r="D10">
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Name 42</t>
+          <t>Name 23</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="D11" s="5">

--- a/teammatch2x3.xlsx
+++ b/teammatch2x3.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 10, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 11, 2026.</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name 53</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="D8">
@@ -548,12 +548,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name 59</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="D9">
@@ -567,12 +567,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 63</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="D10">
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Name 23</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 62</t>
         </is>
       </c>
       <c r="D11" s="5">

--- a/teammatch2x3.xlsx
+++ b/teammatch2x3.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 11, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 18, 2026.</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name 19</t>
+          <t>Name 51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name 44</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="D8">
@@ -548,12 +548,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 76</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 16</t>
         </is>
       </c>
       <c r="D9">
@@ -567,12 +567,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 24</t>
         </is>
       </c>
       <c r="D10">
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Name 84</t>
+          <t>Name 80</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Name 62</t>
+          <t>Name 89</t>
         </is>
       </c>
       <c r="D11" s="5">

--- a/teammatch2x3.xlsx
+++ b/teammatch2x3.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Mar 18, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Mar 20, 2026.</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name 32</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="D8">
@@ -548,12 +548,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Name 76</t>
+          <t>Name 23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name 16</t>
+          <t>Name 81</t>
         </is>
       </c>
       <c r="D9">
@@ -567,12 +567,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 24</t>
+          <t>Name 44</t>
         </is>
       </c>
       <c r="D10">
@@ -586,12 +586,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Name 80</t>
+          <t>Name 69</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Name 89</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="D11" s="5">
